--- a/forms/trg/Formulir_TRG_se-engineering.xlsx
+++ b/forms/trg/Formulir_TRG_se-engineering.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,20 +925,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Miswar Tumpu</t>
+          <t>Prof. Herman Parung</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Civil Engineering | Seismic Design | Composite Structures</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -946,12 +946,12 @@
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6803261</t>
+          <t>5985706</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57215000658</t>
+          <t>55898339200</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nasruddin</t>
+          <t>Dr. Miswar Tumpu</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -987,12 +987,12 @@
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6031701</t>
+          <t>6803261</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57202249456</t>
+          <t>57215000658</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1007,23 +1007,35 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Benny Suryanto, BEng., MEng., Ph.D., FHEA</t>
+          <t>Dr. Nasruddin</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6031701</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57202249456</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1036,12 +1048,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Jamaluddin Bangki</t>
+          <t>Benny Suryanto, BEng., MEng., Ph.D., FHEA</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1065,19 +1077,15 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Armin Aryadi</t>
+          <t>Jamaluddin Bangki</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
@@ -1098,12 +1106,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Bastian Artanto Ampangallo</t>
+          <t>Armin Aryadi</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1131,12 +1139,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Fatriady MR</t>
+          <t>Bastian Artanto Ampangallo</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1164,12 +1172,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Sofyan</t>
+          <t>Fatriady MR</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1197,12 +1205,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Sheren Viola Gloria</t>
+          <t>Muhammad Sofyan</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1230,12 +1238,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Marpaung</t>
+          <t>Sheren Viola Gloria</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1261,10 +1269,26 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Marpaung</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Lorem ipsum dolor sit amet, officia excepteur ex fugiat reprehenderit enim labore culpa sint ad nisi Lorem pariatur mollit ex esse exercitation amet. Nisi anim cupidatat excepteur officia. Reprehenderit nostrud nostrud ipsum Lorem est aliquip amet voluptate voluptate dolor minim nulla est proident. Lorem ipsum dolor sit amet, qui minim labore adipisicing minim sint cillum sint consectetur cupidatat.</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1272,7 +1296,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1461,15 +1489,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
